--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_FCP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_FCP.xlsx
@@ -422,23 +422,342 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>height_cm</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>rpg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>apg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>spg</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tov_pg</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>bpg</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>FCP_T._BROPLEH</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>T. Bropleh</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>30.7</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>C. Allen Williams</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>28.4</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FCP_C._DUNDAO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C. Dundao</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>24.2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FCP_X._WILLIAMS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>X. Williams</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FCP_M._QUEIROZ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>M. Queiroz</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -484,12 +803,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -546,34 +865,102 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>shooting</t>
+          <t>rotation</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>most_used_zone</t>
+          <t>most_used_player</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>T. Bropleh</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>scoring</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>primary_scorer</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>T. Bropleh</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>lineups</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>base_lineup</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C. Allen Williams | C. Dundao | M. Queiroz | T. Bropleh | X. Williams (16.2 min)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>lineups</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>best_lineup</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>C. Allen Williams | C. Dundao | M. Queiroz | T. Bropleh | X. Williams (-7.4 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>shooting</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>most_used_zone</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>shooting</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>best_zone</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
         </is>
       </c>
     </row>
@@ -632,16 +1019,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>79.8</v>
+        <v>78</v>
       </c>
       <c r="C2" t="n">
-        <v>76.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="3">
@@ -651,16 +1038,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>138.2</v>
+        <v>129.5</v>
       </c>
       <c r="C3" t="n">
-        <v>110.4</v>
+        <v>106.2</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>27.8</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="4">
@@ -670,16 +1057,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>116.2</v>
+        <v>115.2</v>
       </c>
       <c r="C4" t="n">
-        <v>110.4</v>
+        <v>106.6</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="5">
@@ -689,16 +1076,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>14.3</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>22</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="6">
@@ -708,16 +1095,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.2</v>
+        <v>16.8</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="7">
@@ -733,10 +1120,10 @@
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
@@ -746,10 +1133,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -765,16 +1152,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>20.5</v>
       </c>
       <c r="C9" t="n">
-        <v>21.3</v>
+        <v>20.8</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="10">
@@ -784,13 +1171,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C10" t="n">
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
         <v>-0.1</v>
@@ -809,7 +1196,7 @@
         <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
         <v>-0</v>
@@ -853,7 +1240,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Above-average pace; expect a game that can speed up if you allow early flow.</t>
+          <t>League-average pace; rhythm control matters more than pure speed against them.</t>
         </is>
       </c>
     </row>
@@ -865,7 +1252,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Above-average assist profile; expect cleaner passing sequences and more extra-pass possessions.</t>
+          <t>Ball movement is close to league average; they can share it but are not purely pass-first.</t>
         </is>
       </c>
     </row>
@@ -889,7 +1276,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Loose enough with the ball to be pressured; there are possessions to steal here.</t>
+          <t>Turnover profile is close to league average; pressure helps, but it is not the whole plan.</t>
         </is>
       </c>
     </row>
@@ -901,7 +1288,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lower foul volume than league average; this is not a team that wants constant contact chaos.</t>
+          <t>Foul profile sits near league average; physicality is part of the game, but not their defining trait.</t>
         </is>
       </c>
     </row>
@@ -913,7 +1300,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Less three-point dependent than league average; more of their offense is built away from pure perimeter volume.</t>
+          <t>Perimeter volume is close to league average; shot mix alone does not define them.</t>
         </is>
       </c>
     </row>
@@ -928,7 +1315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -955,7 +1342,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Set the tempo early: if you let them run into flow, the game can speed up on their terms.</t>
+          <t>Own the rhythm: pace itself is not the main separator, so the quality of possessions matters more than speed.</t>
         </is>
       </c>
     </row>
@@ -979,7 +1366,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Do not overreact to the arc: make them finish over traffic instead of giving up easy paint comfort.</t>
+          <t>Know the first reference: T. Bropleh is a primary scorer, and the plan should start with taking away his comfort.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Game Plan Keys</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Closeout discipline matters: T. Bropleh, X. Williams are the first perimeter names you cannot lose in help situations.</t>
         </is>
       </c>
     </row>
@@ -994,7 +1393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1016,48 +1415,84 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Perimeter Shooting</t>
+          <t>Offense</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from C. Allen Williams and X. Williams; contest, but do not over-help into secondary advantages.</t>
+          <t>The main offensive references are T. Bropleh and C. Allen Williams; load the scouting plan into those names first.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Scoring Areas</t>
+          <t>Perimeter Shooting</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Their offense naturally flows toward Restricted Area; protect that area early in possessions.</t>
+          <t>Priority closeouts start with T. Bropleh and X. Williams; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Scoring Areas</t>
+          <t>Perimeter Shooting</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially M. Queiroz, T. Omlid, and T. Bropleh; force them away from preferred areas.</t>
+          <t>Some perimeter volume comes from C. Allen Williams and C. Dundao; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Scoring Areas</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Their offense naturally flows toward Above the Break 3; protect that area early in possessions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Scoring Areas</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Several players have clear comfort zones, especially T. Bropleh, C. Allen Williams, and G. Delgado; force them away from preferred areas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Defensive Emphasis</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Second-chance threat; the first stop is not enough against this team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Defensive Emphasis</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Do not lose T. Bropleh and X. Williams in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1072,23 +1507,238 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fg3a</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>fg3_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>main_zone</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>role_note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>FCP_T._BROPLEH</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>T. Bropleh</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>61.5%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>primary scorer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>C. Allen Williams</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>13</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>primary handler</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FCP_C._DUNDAO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C. Dundao</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>rotation piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FCP_X._WILLIAMS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>X. Williams</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="D5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>rotation piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FCP_M._QUEIROZ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>M. Queiroz</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>paint finisher</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1197,37 +1847,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FCP_C._ALLEN_WILLIAMS</t>
+          <t>FCP_T._BROPLEH</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C. Allen Williams</t>
+          <t>T. Bropleh</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1243,7 +1893,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1257,23 +1907,23 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -1294,36 +1944,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FCP_C._DUNDAO</t>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C. Dundao</t>
+          <t>C. Allen Williams</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -1335,74 +1985,94 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>31</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>80.6%</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>40.8%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FCP_C._DUNDAO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>C. Dundao</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FCP_J._WOODARD</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>J. Woodard</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>21</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>27.6%</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1420,23 +2090,23 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>29.7%</t>
         </is>
       </c>
     </row>
@@ -1456,23 +2126,23 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>28.4%</t>
         </is>
       </c>
     </row>
@@ -1492,42 +2162,34 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>20.3%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>FCP_M._QUEIROZ</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>M. Queiroz</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
@@ -1536,42 +2198,34 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>13.5%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>FCP_T._OMLID</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>T. Omlid</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -1580,23 +2234,23 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>6.1%</t>
         </is>
       </c>
     </row>
@@ -1628,19 +2282,19 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
     </row>
@@ -1652,12 +2306,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FCP_C._DUNDAO</t>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>C. Dundao</t>
+          <t>C. Allen Williams</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1668,15 +2322,15 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -1684,7 +2338,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>30.8%</t>
         </is>
       </c>
     </row>
@@ -1696,12 +2350,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FCP_C._ALLEN_WILLIAMS</t>
+          <t>FCP_G._DELGADO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>C. Allen Williams</t>
+          <t>G. Delgado</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1712,23 +2366,243 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>7</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>2</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>58.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>FCP_C._DUNDAO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>C. Dundao</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="K14" t="n">
+      <c r="K15" t="n">
+        <v>7</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FCP_T._OMLID</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>T. Omlid</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>6</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>FCP_M._QUEIROZ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>M. Queiroz</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>6</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FCP_J._WOODARD</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>J. Woodard</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
         <v>5</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>20.0%</t>
         </is>
       </c>
-      <c r="M14" t="n">
+      <c r="M18" t="n">
         <v>0.6</v>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>41.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>FCP_X._WILLIAMS</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>X. Williams</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>5</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>26.3%</t>
         </is>
       </c>
     </row>

--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_FCP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_FCP.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -515,36 +515,36 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -567,36 +567,36 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -619,36 +619,36 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -671,41 +671,41 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.3</t>
         </is>
       </c>
     </row>
@@ -723,41 +723,145 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FCP_V._VOYTSO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>V. Voytso</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>19.7</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FCP_J._WOODARD</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>J. Woodard</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>0.0</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -772,24 +876,140 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>players</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>minutes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pf_per40</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pa_per40</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>net_per40</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Most used</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>C. Allen Williams | T. Bropleh</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="F2" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Best defense</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>C. Dundao | T. Bropleh</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="G3" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Best net</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>C. Dundao | T. Bropleh</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>11.8</v>
       </c>
     </row>
   </sheetData>
@@ -909,7 +1129,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>C. Allen Williams | C. Dundao | M. Queiroz | T. Bropleh | X. Williams (16.2 min)</t>
+          <t>C. Allen Williams | C. Dundao | M. Queiroz | T. Bropleh | X. Williams (19.9 min)</t>
         </is>
       </c>
     </row>
@@ -926,7 +1146,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>C. Allen Williams | C. Dundao | M. Queiroz | T. Bropleh | X. Williams (-7.4 net)</t>
+          <t>C. Allen Williams | C. Dundao | M. Queiroz | T. Bropleh | X. Williams (-12.1 net)</t>
         </is>
       </c>
     </row>
@@ -1019,16 +1239,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="C2" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.7</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="3">
@@ -1038,16 +1258,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>129.5</v>
+        <v>125.7</v>
       </c>
       <c r="C3" t="n">
-        <v>106.2</v>
+        <v>105.6</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>23.3</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="4">
@@ -1057,16 +1277,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>115.2</v>
+        <v>115.3</v>
       </c>
       <c r="C4" t="n">
-        <v>106.6</v>
+        <v>105.9</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="5">
@@ -1076,16 +1296,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.3</v>
+        <v>10.4</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>14.7</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="6">
@@ -1095,16 +1315,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>16.8</v>
+        <v>17.4</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="7">
@@ -1120,7 +1340,7 @@
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
         <v>-0</v>
@@ -1133,7 +1353,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="C8" t="n">
         <v>0.3</v>
@@ -1142,7 +1362,7 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -1152,16 +1372,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20.5</v>
+        <v>19.7</v>
       </c>
       <c r="C9" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10">
@@ -1177,10 +1397,10 @@
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="11">
@@ -1196,10 +1416,10 @@
         <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1276,7 +1496,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Turnover profile is close to league average; pressure helps, but it is not the whole plan.</t>
+          <t>Better-than-average ball security; they do not hand away many live possessions.</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1508,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Foul profile sits near league average; physicality is part of the game, but not their defining trait.</t>
+          <t>Lower foul volume than league average; this is not a team that wants constant contact chaos.</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1598,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Closeout discipline matters: T. Bropleh, X. Williams are the first perimeter names you cannot lose in help situations.</t>
+          <t>Closeout discipline matters: T. Bropleh, A. Bessa are the first perimeter names you cannot lose in help situations.</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1432,7 +1652,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priority closeouts start with T. Bropleh and X. Williams; do not lose them in help-and-recover situations.</t>
+          <t>Priority closeouts start with T. Bropleh, A. Bessa, and X. Williams; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1664,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from C. Allen Williams and C. Dundao; contest, but do not over-help into secondary advantages.</t>
+          <t>Some perimeter volume comes from C. Dundao and J. Woodard; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
@@ -1468,19 +1688,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially T. Bropleh, C. Allen Williams, and G. Delgado; force them away from preferred areas.</t>
+          <t>Several players have clear comfort zones, especially C. Allen Williams, T. Bropleh, and A. Bessa; force them away from preferred areas.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Defensive Emphasis</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Second-chance threat; the first stop is not enough against this team.</t>
+          <t>Recognize the main duo/trio combinations: C. Allen Williams | T. Bropleh and C. Dundao | T. Bropleh.</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1712,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Do not lose T. Bropleh and X. Williams in help-and-recover situations.</t>
+          <t>Second-chance threat; the first stop is not enough against this team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Defensive Emphasis</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Do not lose T. Bropleh and A. Bessa in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1574,17 +1806,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>30.7</v>
+        <v>29.4</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>17.7</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1610,22 +1842,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.4</v>
+        <v>28.9</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1646,17 +1878,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24.2</v>
+        <v>22.9</v>
       </c>
       <c r="D4" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1682,17 +1914,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.9</v>
+        <v>22.2</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1702,7 +1934,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>rotation piece</t>
+          <t>bench spacer</t>
         </is>
       </c>
     </row>
@@ -1718,10 +1950,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.4</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -1737,6 +1969,42 @@
         </is>
       </c>
       <c r="H6" t="inlineStr">
+        <is>
+          <t>paint finisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FCP_V._VOYTSO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>V. Voytso</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>paint finisher</t>
         </is>
@@ -1753,7 +2021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1861,23 +2129,23 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1898,29 +2166,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FCP_X._WILLIAMS</t>
+          <t>FCP_A._BESSA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>X. Williams</t>
+          <t>A. Bessa</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H3" t="n">
         <v>1.2</v>
@@ -1939,41 +2207,41 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FCP_C._ALLEN_WILLIAMS</t>
+          <t>FCP_X._WILLIAMS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C. Allen Williams</t>
+          <t>X. Williams</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -1985,25 +2253,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FCP_C._DUNDAO</t>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>C. Dundao</t>
+          <t>C. Allen Williams</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2012,10 +2280,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2036,32 +2304,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FCP_J._WOODARD</t>
+          <t>FCP_C._DUNDAO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>J. Woodard</t>
+          <t>C. Dundao</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2077,38 +2345,48 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FCP_J._WOODARD</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>J. Woodard</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>52.9%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>17</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>44</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>38.6%</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>29.7%</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2126,23 +2404,23 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>31.8%</t>
         </is>
       </c>
     </row>
@@ -2162,23 +2440,23 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>27.6%</t>
         </is>
       </c>
     </row>
@@ -2198,23 +2476,23 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>18.7%</t>
         </is>
       </c>
     </row>
@@ -2234,42 +2512,34 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>12.6%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>FCP_T._BROPLEH</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>T. Bropleh</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
@@ -2278,7 +2548,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -2286,15 +2556,15 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>5.1%</t>
         </is>
       </c>
     </row>
@@ -2322,15 +2592,15 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -2338,7 +2608,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -2350,12 +2620,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FCP_G._DELGADO</t>
+          <t>FCP_T._BROPLEH</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>G. Delgado</t>
+          <t>T. Bropleh</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -2366,23 +2636,23 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>45.2%</t>
         </is>
       </c>
     </row>
@@ -2394,12 +2664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FCP_C._DUNDAO</t>
+          <t>FCP_A._BESSA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>C. Dundao</t>
+          <t>A. Bessa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -2414,19 +2684,19 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>68.8%</t>
         </is>
       </c>
     </row>
@@ -2438,12 +2708,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FCP_T._OMLID</t>
+          <t>FCP_M._QUEIROZ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>T. Omlid</t>
+          <t>M. Queiroz</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -2458,19 +2728,19 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>57.9%</t>
         </is>
       </c>
     </row>
@@ -2482,12 +2752,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FCP_M._QUEIROZ</t>
+          <t>FCP_C._DUNDAO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>M. Queiroz</t>
+          <t>C. Dundao</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -2498,23 +2768,23 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>34.6%</t>
         </is>
       </c>
     </row>
@@ -2546,19 +2816,19 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>47.1%</t>
         </is>
       </c>
     </row>
@@ -2570,12 +2840,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FCP_X._WILLIAMS</t>
+          <t>FCP_G._DELGADO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>X. Williams</t>
+          <t>G. Delgado</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -2586,23 +2856,67 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>58.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>FCP_T._OMLID</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>T. Omlid</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>6</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>75.0%</t>
         </is>
       </c>
     </row>

--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_FCP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_FCP.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -515,36 +515,36 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -567,31 +567,31 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -619,26 +619,26 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -660,188 +660,188 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FCP_X._WILLIAMS</t>
+          <t>FCP_V._VOYTSO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>X. Williams</t>
+          <t>V. Voytso</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FCP_M._QUEIROZ</t>
+          <t>FCP_X._WILLIAMS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M. Queiroz</t>
+          <t>X. Williams</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FCP_V._VOYTSO</t>
+          <t>FCP_J._WOODARD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>V. Voytso</t>
+          <t>J. Woodard</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FCP_J._WOODARD</t>
+          <t>FCP_M._QUEIROZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Woodard</t>
+          <t>M. Queiroz</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -851,15 +851,119 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FCP_G._DELGADO</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>G. Delgado</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>15.2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCP_A._BESSA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A. Bessa</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>14.2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -876,11 +980,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -942,16 +1046,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>59.8</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>101.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>92.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>9.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -962,54 +1066,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Best defense</t>
+          <t>Best net</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C. Dundao | T. Bropleh</t>
+          <t>C. Allen Williams | V. Voytso</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>54.2</v>
+        <v>56.4</v>
       </c>
       <c r="E3" t="n">
-        <v>98.90000000000001</v>
+        <v>102.9</v>
       </c>
       <c r="F3" t="n">
-        <v>87.09999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="G3" t="n">
-        <v>11.8</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>duo</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Best net</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>C. Dundao | T. Bropleh</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="F4" t="n">
-        <v>87.09999999999999</v>
-      </c>
-      <c r="G4" t="n">
-        <v>11.8</v>
+        <v>18.5</v>
       </c>
     </row>
   </sheetData>
@@ -1146,7 +1221,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>C. Allen Williams | C. Dundao | M. Queiroz | T. Bropleh | X. Williams (-12.1 net)</t>
+          <t>C. Dundao | G. Delgado | J. Woodard | T. Omlid | X. Williams (35.8 net)</t>
         </is>
       </c>
     </row>
@@ -1239,16 +1314,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>78.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>78.8</v>
+        <v>79.3</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="3">
@@ -1258,16 +1333,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>125.7</v>
+        <v>123.7</v>
       </c>
       <c r="C3" t="n">
-        <v>105.6</v>
+        <v>103.9</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>20.1</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="4">
@@ -1277,16 +1352,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>115.3</v>
+        <v>114.2</v>
       </c>
       <c r="C4" t="n">
-        <v>105.9</v>
+        <v>104</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>9.4</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="5">
@@ -1296,16 +1371,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.4</v>
+        <v>9.6</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>10.7</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1315,16 +1390,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19.8</v>
       </c>
       <c r="C6" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="7">
@@ -1372,16 +1447,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19.7</v>
+        <v>18.2</v>
       </c>
       <c r="C9" t="n">
         <v>20.7</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>-1</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="10">
@@ -1397,7 +1472,7 @@
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
         <v>-0</v>
@@ -1460,7 +1535,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>League-average pace; rhythm control matters more than pure speed against them.</t>
+          <t>Below-average pace; they are more comfortable when the game stays organized in the half court.</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1547,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ball movement is close to league average; they can share it but are not purely pass-first.</t>
+          <t>Above-average assist profile; expect cleaner passing sequences and more extra-pass possessions.</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1637,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Own the rhythm: pace itself is not the main separator, so the quality of possessions matters more than speed.</t>
+          <t>Control the rhythm: they are more comfortable in a controlled half-court game, so do not let them play cleanly into structure.</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1661,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Know the first reference: T. Bropleh is a primary scorer, and the plan should start with taking away his comfort.</t>
+          <t>Know the first reference: T. Bropleh is a spot-up shooter, and the plan should start with taking away his comfort.</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1673,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Closeout discipline matters: T. Bropleh, A. Bessa are the first perimeter names you cannot lose in help situations.</t>
+          <t>Closeout discipline matters: V. Voytso, T. Bropleh are the first perimeter names you cannot lose in help situations.</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1727,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priority closeouts start with T. Bropleh, A. Bessa, and X. Williams; do not lose them in help-and-recover situations.</t>
+          <t>Priority closeouts start with V. Voytso, T. Bropleh, and A. Bessa; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1763,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially C. Allen Williams, T. Bropleh, and A. Bessa; force them away from preferred areas.</t>
+          <t>Several players have clear comfort zones, especially C. Allen Williams, T. Bropleh, and G. Delgado; force them away from preferred areas.</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1775,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Recognize the main duo/trio combinations: C. Allen Williams | T. Bropleh and C. Dundao | T. Bropleh.</t>
+          <t>Recognize the main duo/trio combinations: C. Allen Williams | T. Bropleh and C. Allen Williams | V. Voytso.</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1799,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Do not lose T. Bropleh and A. Bessa in help-and-recover situations.</t>
+          <t>Do not lose V. Voytso and T. Bropleh in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1806,17 +1881,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>29.4</v>
+        <v>27.2</v>
       </c>
       <c r="D2" t="n">
-        <v>17.7</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1826,7 +1901,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>primary scorer</t>
+          <t>spot-up shooter</t>
         </is>
       </c>
     </row>
@@ -1842,17 +1917,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.9</v>
+        <v>26.9</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>13.8</v>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1878,17 +1953,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.9</v>
+        <v>22.3</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1898,33 +1973,33 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>rotation piece</t>
+          <t>bench spacer</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FCP_X._WILLIAMS</t>
+          <t>FCP_V._VOYTSO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>X. Williams</t>
+          <t>V. Voytso</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.2</v>
+        <v>21.5</v>
       </c>
       <c r="D5" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1941,72 +2016,72 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FCP_M._QUEIROZ</t>
+          <t>FCP_X._WILLIAMS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M. Queiroz</t>
+          <t>X. Williams</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>paint finisher</t>
+          <t>bench spacer</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FCP_V._VOYTSO</t>
+          <t>FCP_J._WOODARD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>V. Voytso</t>
+          <t>J. Woodard</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19.7</v>
+        <v>18.7</v>
       </c>
       <c r="D7" t="n">
-        <v>6.3</v>
+        <v>7.8</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>paint finisher</t>
+          <t>rotation piece</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -2120,32 +2195,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FCP_T._BROPLEH</t>
+          <t>FCP_V._VOYTSO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>T. Bropleh</t>
+          <t>V. Voytso</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2166,32 +2241,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FCP_A._BESSA</t>
+          <t>FCP_T._BROPLEH</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A. Bessa</t>
+          <t>T. Bropleh</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2212,32 +2287,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FCP_X._WILLIAMS</t>
+          <t>FCP_A._BESSA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>X. Williams</t>
+          <t>A. Bessa</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2258,12 +2333,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FCP_C._ALLEN_WILLIAMS</t>
+          <t>FCP_X._WILLIAMS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>C. Allen Williams</t>
+          <t>X. Williams</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -2271,19 +2346,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2313,23 +2388,23 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2359,23 +2434,23 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2391,38 +2466,48 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>68</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>39.7%</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FCP_T._OMLID</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>T. Omlid</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H8" t="n">
         <v>1.2</v>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>31.8%</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2440,23 +2525,23 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -2476,23 +2561,23 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>26.3%</t>
         </is>
       </c>
     </row>
@@ -2512,23 +2597,23 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>18.6%</t>
         </is>
       </c>
     </row>
@@ -2548,42 +2633,34 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>12.6%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>FCP_C._ALLEN_WILLIAMS</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>C. Allen Williams</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
@@ -2592,23 +2669,23 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>4.9%</t>
         </is>
       </c>
     </row>
@@ -2620,12 +2697,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FCP_T._BROPLEH</t>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T. Bropleh</t>
+          <t>C. Allen Williams</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -2640,19 +2717,19 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -2664,12 +2741,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FCP_A._BESSA</t>
+          <t>FCP_T._BROPLEH</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A. Bessa</t>
+          <t>T. Bropleh</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -2684,19 +2761,19 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>45.9%</t>
         </is>
       </c>
     </row>
@@ -2708,12 +2785,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FCP_M._QUEIROZ</t>
+          <t>FCP_G._DELGADO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>M. Queiroz</t>
+          <t>G. Delgado</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -2728,19 +2805,19 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>59.3%</t>
         </is>
       </c>
     </row>
@@ -2752,12 +2829,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FCP_C._DUNDAO</t>
+          <t>FCP_A._BESSA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>C. Dundao</t>
+          <t>A. Bessa</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -2772,19 +2849,19 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>65.0%</t>
         </is>
       </c>
     </row>
@@ -2796,12 +2873,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FCP_J._WOODARD</t>
+          <t>FCP_M._QUEIROZ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>J. Woodard</t>
+          <t>M. Queiroz</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -2812,23 +2889,23 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>57.9%</t>
         </is>
       </c>
     </row>
@@ -2840,12 +2917,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FCP_G._DELGADO</t>
+          <t>FCP_C._DUNDAO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>G. Delgado</t>
+          <t>C. Dundao</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -2856,23 +2933,23 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>32.4%</t>
         </is>
       </c>
     </row>
@@ -2884,12 +2961,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FCP_T._OMLID</t>
+          <t>FCP_J._WOODARD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>T. Omlid</t>
+          <t>J. Woodard</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -2900,23 +2977,67 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>10</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>47.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>FCP_T._OMLID</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>T. Omlid</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="K20" t="n">
-        <v>6</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="M20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N20" t="inlineStr">
+      <c r="K21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>75.0%</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
